--- a/reports/ai_readiness_2026-W25.xlsx
+++ b/reports/ai_readiness_2026-W25.xlsx
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-15 10:57 UTC</t>
+          <t>Generated: 2026-06-15 18:07 UTC</t>
         </is>
       </c>
     </row>
@@ -1044,7 +1044,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-15 10:57 UTC</t>
+          <t>Generated: 2026-06-15 18:07 UTC</t>
         </is>
       </c>
     </row>
